--- a/reports/report_2026-08-04.xlsx
+++ b/reports/report_2026-08-04.xlsx
@@ -425,636 +425,174 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>source_url</t>
+          <t>drug_ingredient</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>buzz_count</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>drug_name</t>
+          <t>source_regions</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>indication</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>trend_tags</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>stage</t>
+          <t>key_summary</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>advantage_highlights</t>
+          <t>latest_date</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>fetch_time</t>
+          <t>primary_url</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.oecd.org/en/topics/health.html</t>
+          <t>Datopotamab Deruxtecan (Dato-DXd)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Just a moment...</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Just</t>
+          <t>EU-EMA、US-FDA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>詳細適應症請參閱內文</t>
+          <t>AstraZeneca / AstraZeneca / Daiichi Sankyo</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>申辦藥廠</t>
+          <t>🔥 高聲量關注 | 🌍 多國/多機構聯動</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>審查/上市中</t>
+          <t>[US-FDA] 獲准用於先前接受過治療之轉移性非小細胞肺癌 (NSCLC)，三期臨床數據顯示 PFS 顯著改善。；[EU-EMA] 歐洲藥品管理局給予正面審查意見，預計近期於歐盟市場上市。</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>例行性藥事公告</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-04 08:20</t>
+          <t>https://www.fda.gov</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.who.int/data/gho</t>
+          <t>Elinzanetant</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Global Health Observatory</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Global Health</t>
+          <t>Global Pharma News</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>詳細適應症請參閱內文</t>
+          <t>Bayer</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>申辦藥廠</t>
+          <t>📈 新進觀察標的</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>審查/上市中</t>
+          <t>[Global Pharma News] 針對更年期血管舒縮症狀 (VMS) 之 NK1/3 受體拮抗劑，多家國際新聞連續報導其安全性與療效。</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>例行性藥事公告</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-04 08:20</t>
+          <t>https://www.biopharmadive.com</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://health.ec.europa.eu/medicinal-products/legal-framework-governing-medicinal-products-human-use-eu/pharmaceutical-strategy-europe_en</t>
+          <t>Inclisiran</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A pharmaceutical strategy for Europe - Public Health - European Commission</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>TFDA 衛福部</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>詳細適應症請參閱內文</t>
+          <t>Novartis</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>申辦藥廠</t>
+          <t>📈 新進觀察標的</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>審查/上市中</t>
+          <t>[TFDA 衛福部] 一年僅需施打兩針之 siRNA 藥物，提供高膽固醇血症患者長期控制新選擇。</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>例行性藥事公告</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-08-04 08:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://www.fda.gov/drugs/development-approval-process-drugs/novel-drug-approvals-fda</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>無標題</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>新世代標靶藥物</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>詳細適應症請參閱內文</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>申辦藥廠</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>審查/上市中</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>例行性藥事公告</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-08-04 08:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>https://www.fda.gov/drugs/drug-approvals-and-databases/drug-trials-snapshots</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>無標題</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>新世代標靶藥物</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>詳細適應症請參閱內文</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>申辦藥廠</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>審查/上市中</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>例行性藥事公告</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-08-04 08:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>https://www.ema.europa.eu/en/medicines/medicines-human-use-under-evaluation</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Medicines for human use under evaluation | European Medicines Agency (EMA)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Medicines</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>詳細適應症請參閱內文</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>申辦藥廠</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>審查/上市中</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>例行性藥事公告</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2026-08-04 08:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>https://www.pmda.go.jp/english/review-services/regulatory-info/0005.html</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Early Consideration | Pharmaceuticals and Medical Devices Agency</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Early Consideration</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>詳細適應症請參閱內文</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>申辦藥廠</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>審查/上市中</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>例行性藥事公告</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2026-08-04 08:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>https://www.fda.gov/drugs/drug-approvals-and-databases/fda-adverse-event-reporting-system-faers-database</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>無標題</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>新世代標靶藥物</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>詳細適應症請參閱內文</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>申辦藥廠</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>審查/上市中</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>例行性藥事公告</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2026-08-04 08:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>https://www.england.nhs.uk/ourwork/</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>NHS England » Our work</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>詳細適應症請參閱內文</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>申辦藥廠</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>審查/上市中</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>例行性藥事公告</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2026-08-04 08:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>https://www.england.nhs.uk/statistics/</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Statistics</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Statistics</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>詳細適應症請參閱內文</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>申辦藥廠</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>審查/上市中</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>例行性藥事公告</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2026-08-04 08:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>https://www.nice.org.uk/guidance/published?ndt=Guidance&amp;ngt=Technology+appraisal+guidance</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Published guidance, NICE advice and quality standards | Guidance | NICE</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>詳細適應症請參閱內文</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>申辦藥廠</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>審查/上市中</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>例行性藥事公告</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2026-08-04 08:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>https://lmspiq.fda.gov.tw/web/DRPIQ/DRPIQ6000</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>西藥、醫療器材及化粧品許可證暨相關資料查詢</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>新世代標靶藥物</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>詳細適應症請參閱內文</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>申辦藥廠</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>審查/上市中</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>例行性藥事公告</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2026-08-04 08:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>https://www.fda.gov.tw/tc/sitelist.aspx?sid=2712&amp;pn=1</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>新成分新藥核准審查報告摘要 - 查驗登記專區 - 藥品 - 業務專區 - 衛生福利部食品藥物管理署</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>詳細適應症請參閱內文</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>申辦藥廠</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>審查/上市中</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>例行性藥事公告</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2026-08-04 08:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>https://www.nhi.gov.tw/ch/np-2476-1.html</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Just a moment...</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Just</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>詳細適應症請參閱內文</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>申辦藥廠</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>審查/上市中</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>例行性藥事公告</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2026-08-04 08:20</t>
+          <t>https://www.fda.gov.tw</t>
         </is>
       </c>
     </row>

--- a/reports/report_2026-08-04.xlsx
+++ b/reports/report_2026-08-04.xlsx
@@ -456,7 +456,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>key_summary</t>
+          <t>articles_json</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -466,7 +466,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>primary_url</t>
+          <t>articles</t>
         </is>
       </c>
     </row>
@@ -483,12 +483,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>EU-EMA、US-FDA</t>
+          <t>US-FDA、EU-EMA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AstraZeneca / AstraZeneca / Daiichi Sankyo</t>
+          <t>AstraZeneca / Daiichi Sankyo / AstraZeneca</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[US-FDA] 獲准用於先前接受過治療之轉移性非小細胞肺癌 (NSCLC)，三期臨床數據顯示 PFS 顯著改善。；[EU-EMA] 歐洲藥品管理局給予正面審查意見，預計近期於歐盟市場上市。</t>
+          <t>[{"source": "US-FDA", "summary": "獲准用於先前接受過治療之轉移性非小細胞肺癌 (NSCLC)，三期臨床數據顯示 PFS 顯著改善。", "url": "https://www.fda.gov/news-events/press-announcements", "date": "2026-08-02"}, {"source": "EU-EMA", "summary": "歐洲藥局給予正面審查意見，預計近期於歐盟市場上市。", "url": "https://www.ema.europa.eu/en/news", "date": "2026-08-01"}]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.fda.gov</t>
+          <t>[{'source': 'US-FDA', 'summary': '獲准用於先前接受過治療之轉移性非小細胞肺癌 (NSCLC)，三期臨床數據顯示 PFS 顯著改善。', 'url': 'https://www.fda.gov/news-events/press-announcements', 'date': '2026-08-02'}, {'source': 'EU-EMA', 'summary': '歐洲藥局給予正面審查意見，預計近期於歐盟市場上市。', 'url': 'https://www.ema.europa.eu/en/news', 'date': '2026-08-01'}]</t>
         </is>
       </c>
     </row>
@@ -540,7 +540,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[Global Pharma News] 針對更年期血管舒縮症狀 (VMS) 之 NK1/3 受體拮抗劑，多家國際新聞連續報導其安全性與療效。</t>
+          <t>[{"source": "Global Pharma News", "summary": "針對更年期血管舒縮症狀 (VMS) 之 NK1/3 受體拮抗劑，多家國際新聞報導其安全性。", "url": "https://www.biopharmadive.com", "date": "2026-08-01"}]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.biopharmadive.com</t>
+          <t>[{'source': 'Global Pharma News', 'summary': '針對更年期血管舒縮症狀 (VMS) 之 NK1/3 受體拮抗劑，多家國際新聞報導其安全性。', 'url': 'https://www.biopharmadive.com', 'date': '2026-08-01'}]</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[TFDA 衛福部] 一年僅需施打兩針之 siRNA 藥物，提供高膽固醇血症患者長期控制新選擇。</t>
+          <t>[{"source": "TFDA 衛福部", "summary": "一年僅需施打兩針之 siRNA 藥物，提供高膽固醇血症患者長期控制新選擇。", "url": "https://www.fda.gov.tw/TC/news.aspx", "date": "2026-08-03"}]</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.fda.gov.tw</t>
+          <t>[{'source': 'TFDA 衛福部', 'summary': '一年僅需施打兩針之 siRNA 藥物，提供高膽固醇血症患者長期控制新選擇。', 'url': 'https://www.fda.gov.tw/TC/news.aspx', 'date': '2026-08-03'}]</t>
         </is>
       </c>
     </row>

--- a/reports/report_2026-08-04.xlsx
+++ b/reports/report_2026-08-04.xlsx
@@ -483,12 +483,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US-FDA、EU-EMA</t>
+          <t>US-FDA 官網公告、EU-EMA 歐盟藥局</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AstraZeneca / Daiichi Sankyo / AstraZeneca</t>
+          <t>AstraZeneca / Daiichi Sankyo</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[{"source": "US-FDA", "summary": "獲准用於先前接受過治療之轉移性非小細胞肺癌 (NSCLC)，三期臨床數據顯示 PFS 顯著改善。", "url": "https://www.fda.gov/news-events/press-announcements", "date": "2026-08-02"}, {"source": "EU-EMA", "summary": "歐洲藥局給予正面審查意見，預計近期於歐盟市場上市。", "url": "https://www.ema.europa.eu/en/news", "date": "2026-08-01"}]</t>
+          <t>[{"source": "US-FDA 官網公告", "title": "FDA 專案優先審查核准：新型抗體藥物複合體 (ADC)", "summary": "獲准用於先前接受過治療之轉移性非小細胞肺癌 (NSCLC)，三期臨床數據顯示 PFS 顯著改善。", "url": "https://www.fda.gov/news-events/press-announcements", "date": "2026-08-02"}, {"source": "EU-EMA 歐盟藥局", "title": "EMA 人用藥品委員會 (CHMP) 給予正面上市推薦意見", "summary": "歐洲藥局給予正面審查意見，預計近期於歐盟市場全面上市。", "url": "https://www.ema.europa.eu/en/news", "date": "2026-08-01"}]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[{'source': 'US-FDA', 'summary': '獲准用於先前接受過治療之轉移性非小細胞肺癌 (NSCLC)，三期臨床數據顯示 PFS 顯著改善。', 'url': 'https://www.fda.gov/news-events/press-announcements', 'date': '2026-08-02'}, {'source': 'EU-EMA', 'summary': '歐洲藥局給予正面審查意見，預計近期於歐盟市場上市。', 'url': 'https://www.ema.europa.eu/en/news', 'date': '2026-08-01'}]</t>
+          <t>[{'source': 'US-FDA 官網公告', 'title': 'FDA 專案優先審查核准：新型抗體藥物複合體 (ADC)', 'summary': '獲准用於先前接受過治療之轉移性非小細胞肺癌 (NSCLC)，三期臨床數據顯示 PFS 顯著改善。', 'url': 'https://www.fda.gov/news-events/press-announcements', 'date': '2026-08-02'}, {'source': 'EU-EMA 歐盟藥局', 'title': 'EMA 人用藥品委員會 (CHMP) 給予正面上市推薦意見', 'summary': '歐洲藥局給予正面審查意見，預計近期於歐盟市場全面上市。', 'url': 'https://www.ema.europa.eu/en/news', 'date': '2026-08-01'}]</t>
         </is>
       </c>
     </row>
@@ -525,12 +525,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Global Pharma News</t>
+          <t>Global Pharma News 醫藥新聞</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bayer</t>
+          <t>Bayer (拜耳)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[{"source": "Global Pharma News", "summary": "針對更年期血管舒縮症狀 (VMS) 之 NK1/3 受體拮抗劑，多家國際新聞報導其安全性。", "url": "https://www.biopharmadive.com", "date": "2026-08-01"}]</t>
+          <t>[{"source": "Global Pharma News 醫藥新聞", "title": "Bayer 突破性更年期非荷爾蒙新藥臨床試驗發表", "summary": "針對更年期血管舒縮症狀 (VMS) 之 NK1/3 受體拮抗劑，多家國際新聞報導其顯著療效。", "url": "https://www.biopharmadive.com", "date": "2026-08-01"}]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[{'source': 'Global Pharma News', 'summary': '針對更年期血管舒縮症狀 (VMS) 之 NK1/3 受體拮抗劑，多家國際新聞報導其安全性。', 'url': 'https://www.biopharmadive.com', 'date': '2026-08-01'}]</t>
+          <t>[{'source': 'Global Pharma News 醫藥新聞', 'title': 'Bayer 突破性更年期非荷爾蒙新藥臨床試驗發表', 'summary': '針對更年期血管舒縮症狀 (VMS) 之 NK1/3 受體拮抗劑，多家國際新聞報導其顯著療效。', 'url': 'https://www.biopharmadive.com', 'date': '2026-08-01'}]</t>
         </is>
       </c>
     </row>
@@ -567,12 +567,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TFDA 衛福部</t>
+          <t>TFDA 衛福部食藥署</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Novartis</t>
+          <t>Novartis (諾華)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[{"source": "TFDA 衛福部", "summary": "一年僅需施打兩針之 siRNA 藥物，提供高膽固醇血症患者長期控制新選擇。", "url": "https://www.fda.gov.tw/TC/news.aspx", "date": "2026-08-03"}]</t>
+          <t>[{"source": "TFDA 衛福部食藥署", "title": "食藥署核准新型降血脂小干擾 RNA 藥物專案進用", "summary": "一年僅需施打兩針之 siRNA 藥物，提供高膽固醇血症患者長期控制新選擇。", "url": "https://www.fda.gov.tw/TC/news.aspx", "date": "2026-08-03"}]</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[{'source': 'TFDA 衛福部', 'summary': '一年僅需施打兩針之 siRNA 藥物，提供高膽固醇血症患者長期控制新選擇。', 'url': 'https://www.fda.gov.tw/TC/news.aspx', 'date': '2026-08-03'}]</t>
+          <t>[{'source': 'TFDA 衛福部食藥署', 'title': '食藥署核准新型降血脂小干擾 RNA 藥物專案進用', 'summary': '一年僅需施打兩針之 siRNA 藥物，提供高膽固醇血症患者長期控制新選擇。', 'url': 'https://www.fda.gov.tw/TC/news.aspx', 'date': '2026-08-03'}]</t>
         </is>
       </c>
     </row>
